--- a/course-design-2/outputs/tables/ch8/42_stage26_2_unified_generalization.xlsx
+++ b/course-design-2/outputs/tables/ch8/42_stage26_2_unified_generalization.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_统一协议三种划分" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_CompanyGroup阈值来源" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_多种子明细" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_多种子汇总" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_多种子结论" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_CompanyGroup5次划分" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_CompanyGroup汇总" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="01_统一协议三种划分" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_CompanyGroup阈值来源" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03_多种子明细" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="04_多种子汇总" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="05_多种子结论" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="06_CompanyGroup5次划分" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="07_CompanyGroup汇总" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -517,22 +517,22 @@
         <v>2233</v>
       </c>
       <c r="E2" t="n">
-        <v>36.074723</v>
+        <v>36.099666</v>
       </c>
       <c r="F2" t="n">
-        <v>66.307726</v>
+        <v>66.191014</v>
       </c>
       <c r="G2" t="n">
-        <v>0.562671</v>
+        <v>0.564209</v>
       </c>
       <c r="H2" t="n">
-        <v>36.088217</v>
+        <v>36.206167</v>
       </c>
       <c r="I2" t="n">
-        <v>69.294882</v>
+        <v>69.574967</v>
       </c>
       <c r="J2" t="n">
-        <v>0.596413</v>
+        <v>0.593144</v>
       </c>
       <c r="K2" t="n">
         <v>320</v>
@@ -562,22 +562,22 @@
         <v>1688</v>
       </c>
       <c r="E3" t="n">
-        <v>52.049937</v>
+        <v>52.074078</v>
       </c>
       <c r="F3" t="n">
-        <v>103.833935</v>
+        <v>103.807537</v>
       </c>
       <c r="G3" t="n">
-        <v>0.131513</v>
+        <v>0.131955</v>
       </c>
       <c r="H3" t="n">
-        <v>56.962223</v>
+        <v>56.674976</v>
       </c>
       <c r="I3" t="n">
-        <v>99.806539</v>
+        <v>99.701494</v>
       </c>
       <c r="J3" t="n">
-        <v>0.144818</v>
+        <v>0.146617</v>
       </c>
       <c r="K3" t="n">
         <v>310</v>
@@ -607,22 +607,22 @@
         <v>2398</v>
       </c>
       <c r="E4" t="n">
-        <v>31.725791</v>
+        <v>32.048155</v>
       </c>
       <c r="F4" t="n">
-        <v>47.933205</v>
+        <v>48.431642</v>
       </c>
       <c r="G4" t="n">
-        <v>0.651713</v>
+        <v>0.644432</v>
       </c>
       <c r="H4" t="n">
-        <v>39.423584</v>
+        <v>39.548066</v>
       </c>
       <c r="I4" t="n">
-        <v>73.163721</v>
+        <v>72.71595499999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.497337</v>
+        <v>0.503471</v>
       </c>
       <c r="K4" t="n">
         <v>321</v>
@@ -711,16 +711,16 @@
         <v>336</v>
       </c>
       <c r="E2" t="n">
-        <v>56.567882</v>
+        <v>56.695865</v>
       </c>
       <c r="F2" t="n">
-        <v>51.752004</v>
+        <v>52.18975</v>
       </c>
       <c r="G2" t="n">
-        <v>103.025406</v>
+        <v>103.870756</v>
       </c>
       <c r="H2" t="n">
-        <v>0.144986</v>
+        <v>0.130897</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -742,16 +742,16 @@
         <v>310</v>
       </c>
       <c r="E3" t="n">
-        <v>56.962223</v>
+        <v>56.674976</v>
       </c>
       <c r="F3" t="n">
-        <v>52.049937</v>
+        <v>52.074078</v>
       </c>
       <c r="G3" t="n">
-        <v>103.833935</v>
+        <v>103.807537</v>
       </c>
       <c r="H3" t="n">
-        <v>0.131513</v>
+        <v>0.131955</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -835,22 +835,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36.088217</v>
+        <v>36.206167</v>
       </c>
       <c r="D2" t="n">
-        <v>69.294882</v>
+        <v>69.574967</v>
       </c>
       <c r="E2" t="n">
-        <v>0.596413</v>
+        <v>0.593144</v>
       </c>
       <c r="F2" t="n">
-        <v>36.074723</v>
+        <v>36.099666</v>
       </c>
       <c r="G2" t="n">
-        <v>66.307726</v>
+        <v>66.191014</v>
       </c>
       <c r="H2" t="n">
-        <v>0.562671</v>
+        <v>0.564209</v>
       </c>
       <c r="I2" t="n">
         <v>2232</v>
@@ -869,22 +869,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36.678336</v>
+        <v>36.677215</v>
       </c>
       <c r="D3" t="n">
-        <v>68.642066</v>
+        <v>68.938822</v>
       </c>
       <c r="E3" t="n">
-        <v>0.603981</v>
+        <v>0.60055</v>
       </c>
       <c r="F3" t="n">
-        <v>36.275629</v>
+        <v>36.34304</v>
       </c>
       <c r="G3" t="n">
-        <v>64.46742399999999</v>
+        <v>64.751227</v>
       </c>
       <c r="H3" t="n">
-        <v>0.586609</v>
+        <v>0.582962</v>
       </c>
       <c r="I3" t="n">
         <v>2232</v>
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>35.190655</v>
+        <v>34.701769</v>
       </c>
       <c r="D4" t="n">
-        <v>59.257796</v>
+        <v>58.531284</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6332140000000001</v>
+        <v>0.642153</v>
       </c>
       <c r="F4" t="n">
-        <v>35.134067</v>
+        <v>35.326615</v>
       </c>
       <c r="G4" t="n">
-        <v>62.973858</v>
+        <v>62.869497</v>
       </c>
       <c r="H4" t="n">
-        <v>0.591317</v>
+        <v>0.59267</v>
       </c>
       <c r="I4" t="n">
         <v>2232</v>
@@ -937,22 +937,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>36.051069</v>
+        <v>36.000814</v>
       </c>
       <c r="D5" t="n">
-        <v>59.626702</v>
+        <v>59.05052</v>
       </c>
       <c r="E5" t="n">
-        <v>0.628633</v>
+        <v>0.635776</v>
       </c>
       <c r="F5" t="n">
-        <v>36.292945</v>
+        <v>36.422668</v>
       </c>
       <c r="G5" t="n">
-        <v>63.697862</v>
+        <v>63.411971</v>
       </c>
       <c r="H5" t="n">
-        <v>0.581865</v>
+        <v>0.58561</v>
       </c>
       <c r="I5" t="n">
         <v>2232</v>
@@ -971,22 +971,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34.40132</v>
+        <v>34.330348</v>
       </c>
       <c r="D6" t="n">
-        <v>55.973048</v>
+        <v>56.111493</v>
       </c>
       <c r="E6" t="n">
-        <v>0.64523</v>
+        <v>0.643472</v>
       </c>
       <c r="F6" t="n">
-        <v>35.620228</v>
+        <v>35.465991</v>
       </c>
       <c r="G6" t="n">
-        <v>64.29326500000001</v>
+        <v>64.358941</v>
       </c>
       <c r="H6" t="n">
-        <v>0.583522</v>
+        <v>0.58267</v>
       </c>
       <c r="I6" t="n">
         <v>2232</v>
@@ -1005,22 +1005,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>35.227539</v>
+        <v>35.160431</v>
       </c>
       <c r="D7" t="n">
-        <v>56.091187</v>
+        <v>55.854026</v>
       </c>
       <c r="E7" t="n">
-        <v>0.64373</v>
+        <v>0.646737</v>
       </c>
       <c r="F7" t="n">
-        <v>35.750048</v>
+        <v>35.913566</v>
       </c>
       <c r="G7" t="n">
-        <v>62.534048</v>
+        <v>62.803844</v>
       </c>
       <c r="H7" t="n">
-        <v>0.606002</v>
+        <v>0.602595</v>
       </c>
       <c r="I7" t="n">
         <v>2232</v>
@@ -1039,22 +1039,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>35.60711</v>
+        <v>35.7017</v>
       </c>
       <c r="D8" t="n">
-        <v>57.504507</v>
+        <v>57.964418</v>
       </c>
       <c r="E8" t="n">
-        <v>0.624018</v>
+        <v>0.61798</v>
       </c>
       <c r="F8" t="n">
-        <v>34.720444</v>
+        <v>34.874143</v>
       </c>
       <c r="G8" t="n">
-        <v>59.213958</v>
+        <v>58.913839</v>
       </c>
       <c r="H8" t="n">
-        <v>0.691015</v>
+        <v>0.69414</v>
       </c>
       <c r="I8" t="n">
         <v>2232</v>
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>35.774862</v>
+        <v>35.703915</v>
       </c>
       <c r="D9" t="n">
-        <v>57.144841</v>
+        <v>57.47597</v>
       </c>
       <c r="E9" t="n">
-        <v>0.628706</v>
+        <v>0.624391</v>
       </c>
       <c r="F9" t="n">
-        <v>35.286714</v>
+        <v>35.576549</v>
       </c>
       <c r="G9" t="n">
-        <v>59.302294</v>
+        <v>59.030589</v>
       </c>
       <c r="H9" t="n">
-        <v>0.690093</v>
+        <v>0.692926</v>
       </c>
       <c r="I9" t="n">
         <v>2232</v>
@@ -1107,22 +1107,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37.487087</v>
+        <v>37.314144</v>
       </c>
       <c r="D10" t="n">
-        <v>70.46484100000001</v>
+        <v>70.685323</v>
       </c>
       <c r="E10" t="n">
-        <v>0.579162</v>
+        <v>0.576524</v>
       </c>
       <c r="F10" t="n">
-        <v>36.444148</v>
+        <v>36.161685</v>
       </c>
       <c r="G10" t="n">
-        <v>66.56919499999999</v>
+        <v>67.716284</v>
       </c>
       <c r="H10" t="n">
-        <v>0.571252</v>
+        <v>0.556349</v>
       </c>
       <c r="I10" t="n">
         <v>2232</v>
@@ -1141,22 +1141,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38.464724</v>
+        <v>38.354141</v>
       </c>
       <c r="D11" t="n">
-        <v>72.585787</v>
+        <v>72.428774</v>
       </c>
       <c r="E11" t="n">
-        <v>0.553446</v>
+        <v>0.555376</v>
       </c>
       <c r="F11" t="n">
-        <v>36.696204</v>
+        <v>36.525992</v>
       </c>
       <c r="G11" t="n">
-        <v>67.33223</v>
+        <v>67.103229</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5613669999999999</v>
+        <v>0.564346</v>
       </c>
       <c r="I11" t="n">
         <v>2232</v>
@@ -1241,28 +1241,28 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>35.754878</v>
+        <v>35.650826</v>
       </c>
       <c r="D2" t="n">
-        <v>1.149344</v>
+        <v>1.196034</v>
       </c>
       <c r="E2" t="n">
-        <v>62.499015</v>
+        <v>62.573497</v>
       </c>
       <c r="F2" t="n">
-        <v>6.849764</v>
+        <v>6.967117</v>
       </c>
       <c r="G2" t="n">
-        <v>0.615607</v>
+        <v>0.614655</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02718</v>
+        <v>0.029641</v>
       </c>
       <c r="I2" t="n">
-        <v>35.598722</v>
+        <v>35.58562</v>
       </c>
       <c r="J2" t="n">
-        <v>0.694453</v>
+        <v>0.543987</v>
       </c>
     </row>
     <row r="3">
@@ -1275,28 +1275,28 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>36.439306</v>
+        <v>36.379303</v>
       </c>
       <c r="D3" t="n">
-        <v>1.247001</v>
+        <v>1.232253</v>
       </c>
       <c r="E3" t="n">
-        <v>62.818117</v>
+        <v>62.749622</v>
       </c>
       <c r="F3" t="n">
-        <v>7.364586</v>
+        <v>7.433643</v>
       </c>
       <c r="G3" t="n">
-        <v>0.611699</v>
+        <v>0.6125660000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.035549</v>
+        <v>0.036267</v>
       </c>
       <c r="I3" t="n">
-        <v>36.060308</v>
+        <v>36.156363</v>
       </c>
       <c r="J3" t="n">
-        <v>0.547621</v>
+        <v>0.399226</v>
       </c>
     </row>
   </sheetData>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>35.7549 ± 1.1493</t>
+          <t>35.6508 ± 1.1960</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>36.4393 ± 1.2470</t>
+          <t>36.3793 ± 1.2323</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1437,16 +1437,16 @@
         <v>1688</v>
       </c>
       <c r="E2" t="n">
-        <v>52.049937</v>
+        <v>52.074078</v>
       </c>
       <c r="F2" t="n">
-        <v>103.833935</v>
+        <v>103.807537</v>
       </c>
       <c r="G2" t="n">
-        <v>0.131513</v>
+        <v>0.131955</v>
       </c>
       <c r="H2" t="n">
-        <v>56.962223</v>
+        <v>56.674976</v>
       </c>
     </row>
     <row r="3">
@@ -1463,16 +1463,16 @@
         <v>2842</v>
       </c>
       <c r="E3" t="n">
-        <v>80.93106899999999</v>
+        <v>81.340687</v>
       </c>
       <c r="F3" t="n">
-        <v>122.024619</v>
+        <v>122.739735</v>
       </c>
       <c r="G3" t="n">
-        <v>0.010606</v>
+        <v>-0.001025</v>
       </c>
       <c r="H3" t="n">
-        <v>43.254322</v>
+        <v>42.870105</v>
       </c>
     </row>
     <row r="4">
@@ -1489,16 +1489,16 @@
         <v>1988</v>
       </c>
       <c r="E4" t="n">
-        <v>39.401661</v>
+        <v>38.610142</v>
       </c>
       <c r="F4" t="n">
-        <v>62.441205</v>
+        <v>61.390034</v>
       </c>
       <c r="G4" t="n">
-        <v>0.137196</v>
+        <v>0.166001</v>
       </c>
       <c r="H4" t="n">
-        <v>48.093997</v>
+        <v>48.160028</v>
       </c>
     </row>
     <row r="5">
@@ -1515,16 +1515,16 @@
         <v>1867</v>
       </c>
       <c r="E5" t="n">
-        <v>50.965207</v>
+        <v>50.383913</v>
       </c>
       <c r="F5" t="n">
-        <v>102.586407</v>
+        <v>103.129985</v>
       </c>
       <c r="G5" t="n">
-        <v>0.101697</v>
+        <v>0.092152</v>
       </c>
       <c r="H5" t="n">
-        <v>45.072193</v>
+        <v>44.608402</v>
       </c>
     </row>
     <row r="6">
@@ -1541,16 +1541,16 @@
         <v>1870</v>
       </c>
       <c r="E6" t="n">
-        <v>46.648119</v>
+        <v>47.136732</v>
       </c>
       <c r="F6" t="n">
-        <v>79.752487</v>
+        <v>80.124527</v>
       </c>
       <c r="G6" t="n">
-        <v>0.08620800000000001</v>
+        <v>0.077663</v>
       </c>
       <c r="H6" t="n">
-        <v>44.436069</v>
+        <v>44.759939</v>
       </c>
     </row>
   </sheetData>
@@ -1612,25 +1612,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.9992 ± 15.8545</t>
+          <t>53.9091 ± 16.1880</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>94.1277 ± 23.2093</t>
+          <t>94.2384 ± 23.7759</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.093444 ± 0.050858</t>
+          <t>0.093349 ± 0.063093</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>36.074723</v>
+        <v>36.099666</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>39.4017 ~ 80.9311</t>
+          <t>38.6101 ~ 81.3407</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">

--- a/course-design-2/outputs/tables/ch8/42_stage26_2_unified_generalization.xlsx
+++ b/course-design-2/outputs/tables/ch8/42_stage26_2_unified_generalization.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="01_统一协议三种划分" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_CompanyGroup阈值来源" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_多种子明细" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="04_多种子汇总" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="05_多种子结论" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="06_CompanyGroup5次划分" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="07_CompanyGroup汇总" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_统一协议三种划分" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_CompanyGroup阈值来源" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_多种子明细" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_多种子汇总" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_多种子结论" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_CompanyGroup5次划分" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_CompanyGroup汇总" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -517,22 +517,22 @@
         <v>2233</v>
       </c>
       <c r="E2" t="n">
-        <v>36.099666</v>
+        <v>36.074723</v>
       </c>
       <c r="F2" t="n">
-        <v>66.191014</v>
+        <v>66.307726</v>
       </c>
       <c r="G2" t="n">
-        <v>0.564209</v>
+        <v>0.562671</v>
       </c>
       <c r="H2" t="n">
-        <v>36.206167</v>
+        <v>36.088217</v>
       </c>
       <c r="I2" t="n">
-        <v>69.574967</v>
+        <v>69.294882</v>
       </c>
       <c r="J2" t="n">
-        <v>0.593144</v>
+        <v>0.596413</v>
       </c>
       <c r="K2" t="n">
         <v>320</v>
@@ -562,22 +562,22 @@
         <v>1688</v>
       </c>
       <c r="E3" t="n">
-        <v>52.074078</v>
+        <v>52.049937</v>
       </c>
       <c r="F3" t="n">
-        <v>103.807537</v>
+        <v>103.833935</v>
       </c>
       <c r="G3" t="n">
-        <v>0.131955</v>
+        <v>0.131513</v>
       </c>
       <c r="H3" t="n">
-        <v>56.674976</v>
+        <v>56.962223</v>
       </c>
       <c r="I3" t="n">
-        <v>99.701494</v>
+        <v>99.806539</v>
       </c>
       <c r="J3" t="n">
-        <v>0.146617</v>
+        <v>0.144818</v>
       </c>
       <c r="K3" t="n">
         <v>310</v>
@@ -607,22 +607,22 @@
         <v>2398</v>
       </c>
       <c r="E4" t="n">
-        <v>32.048155</v>
+        <v>31.725791</v>
       </c>
       <c r="F4" t="n">
-        <v>48.431642</v>
+        <v>47.933205</v>
       </c>
       <c r="G4" t="n">
-        <v>0.644432</v>
+        <v>0.651713</v>
       </c>
       <c r="H4" t="n">
-        <v>39.548066</v>
+        <v>39.423584</v>
       </c>
       <c r="I4" t="n">
-        <v>72.71595499999999</v>
+        <v>73.163721</v>
       </c>
       <c r="J4" t="n">
-        <v>0.503471</v>
+        <v>0.497337</v>
       </c>
       <c r="K4" t="n">
         <v>321</v>
@@ -711,16 +711,16 @@
         <v>336</v>
       </c>
       <c r="E2" t="n">
-        <v>56.695865</v>
+        <v>56.567882</v>
       </c>
       <c r="F2" t="n">
-        <v>52.18975</v>
+        <v>51.752004</v>
       </c>
       <c r="G2" t="n">
-        <v>103.870756</v>
+        <v>103.025406</v>
       </c>
       <c r="H2" t="n">
-        <v>0.130897</v>
+        <v>0.144986</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -742,16 +742,16 @@
         <v>310</v>
       </c>
       <c r="E3" t="n">
-        <v>56.674976</v>
+        <v>56.962223</v>
       </c>
       <c r="F3" t="n">
-        <v>52.074078</v>
+        <v>52.049937</v>
       </c>
       <c r="G3" t="n">
-        <v>103.807537</v>
+        <v>103.833935</v>
       </c>
       <c r="H3" t="n">
-        <v>0.131955</v>
+        <v>0.131513</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -835,22 +835,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36.206167</v>
+        <v>36.088217</v>
       </c>
       <c r="D2" t="n">
-        <v>69.574967</v>
+        <v>69.294882</v>
       </c>
       <c r="E2" t="n">
-        <v>0.593144</v>
+        <v>0.596413</v>
       </c>
       <c r="F2" t="n">
-        <v>36.099666</v>
+        <v>36.074723</v>
       </c>
       <c r="G2" t="n">
-        <v>66.191014</v>
+        <v>66.307726</v>
       </c>
       <c r="H2" t="n">
-        <v>0.564209</v>
+        <v>0.562671</v>
       </c>
       <c r="I2" t="n">
         <v>2232</v>
@@ -869,22 +869,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36.677215</v>
+        <v>36.678336</v>
       </c>
       <c r="D3" t="n">
-        <v>68.938822</v>
+        <v>68.642066</v>
       </c>
       <c r="E3" t="n">
-        <v>0.60055</v>
+        <v>0.603981</v>
       </c>
       <c r="F3" t="n">
-        <v>36.34304</v>
+        <v>36.275629</v>
       </c>
       <c r="G3" t="n">
-        <v>64.751227</v>
+        <v>64.46742399999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.582962</v>
+        <v>0.586609</v>
       </c>
       <c r="I3" t="n">
         <v>2232</v>
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>34.701769</v>
+        <v>35.190655</v>
       </c>
       <c r="D4" t="n">
-        <v>58.531284</v>
+        <v>59.257796</v>
       </c>
       <c r="E4" t="n">
-        <v>0.642153</v>
+        <v>0.6332140000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>35.326615</v>
+        <v>35.134067</v>
       </c>
       <c r="G4" t="n">
-        <v>62.869497</v>
+        <v>62.973858</v>
       </c>
       <c r="H4" t="n">
-        <v>0.59267</v>
+        <v>0.591317</v>
       </c>
       <c r="I4" t="n">
         <v>2232</v>
@@ -937,22 +937,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>36.000814</v>
+        <v>36.051069</v>
       </c>
       <c r="D5" t="n">
-        <v>59.05052</v>
+        <v>59.626702</v>
       </c>
       <c r="E5" t="n">
-        <v>0.635776</v>
+        <v>0.628633</v>
       </c>
       <c r="F5" t="n">
-        <v>36.422668</v>
+        <v>36.292945</v>
       </c>
       <c r="G5" t="n">
-        <v>63.411971</v>
+        <v>63.697862</v>
       </c>
       <c r="H5" t="n">
-        <v>0.58561</v>
+        <v>0.581865</v>
       </c>
       <c r="I5" t="n">
         <v>2232</v>
@@ -971,22 +971,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34.330348</v>
+        <v>34.40132</v>
       </c>
       <c r="D6" t="n">
-        <v>56.111493</v>
+        <v>55.973048</v>
       </c>
       <c r="E6" t="n">
-        <v>0.643472</v>
+        <v>0.64523</v>
       </c>
       <c r="F6" t="n">
-        <v>35.465991</v>
+        <v>35.620228</v>
       </c>
       <c r="G6" t="n">
-        <v>64.358941</v>
+        <v>64.29326500000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.58267</v>
+        <v>0.583522</v>
       </c>
       <c r="I6" t="n">
         <v>2232</v>
@@ -1005,22 +1005,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>35.160431</v>
+        <v>35.227539</v>
       </c>
       <c r="D7" t="n">
-        <v>55.854026</v>
+        <v>56.091187</v>
       </c>
       <c r="E7" t="n">
-        <v>0.646737</v>
+        <v>0.64373</v>
       </c>
       <c r="F7" t="n">
-        <v>35.913566</v>
+        <v>35.750048</v>
       </c>
       <c r="G7" t="n">
-        <v>62.803844</v>
+        <v>62.534048</v>
       </c>
       <c r="H7" t="n">
-        <v>0.602595</v>
+        <v>0.606002</v>
       </c>
       <c r="I7" t="n">
         <v>2232</v>
@@ -1039,22 +1039,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>35.7017</v>
+        <v>35.60711</v>
       </c>
       <c r="D8" t="n">
-        <v>57.964418</v>
+        <v>57.504507</v>
       </c>
       <c r="E8" t="n">
-        <v>0.61798</v>
+        <v>0.624018</v>
       </c>
       <c r="F8" t="n">
-        <v>34.874143</v>
+        <v>34.720444</v>
       </c>
       <c r="G8" t="n">
-        <v>58.913839</v>
+        <v>59.213958</v>
       </c>
       <c r="H8" t="n">
-        <v>0.69414</v>
+        <v>0.691015</v>
       </c>
       <c r="I8" t="n">
         <v>2232</v>
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>35.703915</v>
+        <v>35.774862</v>
       </c>
       <c r="D9" t="n">
-        <v>57.47597</v>
+        <v>57.144841</v>
       </c>
       <c r="E9" t="n">
-        <v>0.624391</v>
+        <v>0.628706</v>
       </c>
       <c r="F9" t="n">
-        <v>35.576549</v>
+        <v>35.286714</v>
       </c>
       <c r="G9" t="n">
-        <v>59.030589</v>
+        <v>59.302294</v>
       </c>
       <c r="H9" t="n">
-        <v>0.692926</v>
+        <v>0.690093</v>
       </c>
       <c r="I9" t="n">
         <v>2232</v>
@@ -1107,22 +1107,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37.314144</v>
+        <v>37.487087</v>
       </c>
       <c r="D10" t="n">
-        <v>70.685323</v>
+        <v>70.46484100000001</v>
       </c>
       <c r="E10" t="n">
-        <v>0.576524</v>
+        <v>0.579162</v>
       </c>
       <c r="F10" t="n">
-        <v>36.161685</v>
+        <v>36.444148</v>
       </c>
       <c r="G10" t="n">
-        <v>67.716284</v>
+        <v>66.56919499999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.556349</v>
+        <v>0.571252</v>
       </c>
       <c r="I10" t="n">
         <v>2232</v>
@@ -1141,22 +1141,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38.354141</v>
+        <v>38.464724</v>
       </c>
       <c r="D11" t="n">
-        <v>72.428774</v>
+        <v>72.585787</v>
       </c>
       <c r="E11" t="n">
-        <v>0.555376</v>
+        <v>0.553446</v>
       </c>
       <c r="F11" t="n">
-        <v>36.525992</v>
+        <v>36.696204</v>
       </c>
       <c r="G11" t="n">
-        <v>67.103229</v>
+        <v>67.33223</v>
       </c>
       <c r="H11" t="n">
-        <v>0.564346</v>
+        <v>0.5613669999999999</v>
       </c>
       <c r="I11" t="n">
         <v>2232</v>
@@ -1241,28 +1241,28 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>35.650826</v>
+        <v>35.754878</v>
       </c>
       <c r="D2" t="n">
-        <v>1.196034</v>
+        <v>1.149344</v>
       </c>
       <c r="E2" t="n">
-        <v>62.573497</v>
+        <v>62.499015</v>
       </c>
       <c r="F2" t="n">
-        <v>6.967117</v>
+        <v>6.849764</v>
       </c>
       <c r="G2" t="n">
-        <v>0.614655</v>
+        <v>0.615607</v>
       </c>
       <c r="H2" t="n">
-        <v>0.029641</v>
+        <v>0.02718</v>
       </c>
       <c r="I2" t="n">
-        <v>35.58562</v>
+        <v>35.598722</v>
       </c>
       <c r="J2" t="n">
-        <v>0.543987</v>
+        <v>0.694453</v>
       </c>
     </row>
     <row r="3">
@@ -1275,28 +1275,28 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>36.379303</v>
+        <v>36.439306</v>
       </c>
       <c r="D3" t="n">
-        <v>1.232253</v>
+        <v>1.247001</v>
       </c>
       <c r="E3" t="n">
-        <v>62.749622</v>
+        <v>62.818117</v>
       </c>
       <c r="F3" t="n">
-        <v>7.433643</v>
+        <v>7.364586</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6125660000000001</v>
+        <v>0.611699</v>
       </c>
       <c r="H3" t="n">
-        <v>0.036267</v>
+        <v>0.035549</v>
       </c>
       <c r="I3" t="n">
-        <v>36.156363</v>
+        <v>36.060308</v>
       </c>
       <c r="J3" t="n">
-        <v>0.399226</v>
+        <v>0.547621</v>
       </c>
     </row>
   </sheetData>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>35.6508 ± 1.1960</t>
+          <t>35.7549 ± 1.1493</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>36.3793 ± 1.2323</t>
+          <t>36.4393 ± 1.2470</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1437,16 +1437,16 @@
         <v>1688</v>
       </c>
       <c r="E2" t="n">
-        <v>52.074078</v>
+        <v>52.049937</v>
       </c>
       <c r="F2" t="n">
-        <v>103.807537</v>
+        <v>103.833935</v>
       </c>
       <c r="G2" t="n">
-        <v>0.131955</v>
+        <v>0.131513</v>
       </c>
       <c r="H2" t="n">
-        <v>56.674976</v>
+        <v>56.962223</v>
       </c>
     </row>
     <row r="3">
@@ -1463,16 +1463,16 @@
         <v>2842</v>
       </c>
       <c r="E3" t="n">
-        <v>81.340687</v>
+        <v>80.93106899999999</v>
       </c>
       <c r="F3" t="n">
-        <v>122.739735</v>
+        <v>122.024619</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.001025</v>
+        <v>0.010606</v>
       </c>
       <c r="H3" t="n">
-        <v>42.870105</v>
+        <v>43.254322</v>
       </c>
     </row>
     <row r="4">
@@ -1489,16 +1489,16 @@
         <v>1988</v>
       </c>
       <c r="E4" t="n">
-        <v>38.610142</v>
+        <v>39.401661</v>
       </c>
       <c r="F4" t="n">
-        <v>61.390034</v>
+        <v>62.441205</v>
       </c>
       <c r="G4" t="n">
-        <v>0.166001</v>
+        <v>0.137196</v>
       </c>
       <c r="H4" t="n">
-        <v>48.160028</v>
+        <v>48.093997</v>
       </c>
     </row>
     <row r="5">
@@ -1515,16 +1515,16 @@
         <v>1867</v>
       </c>
       <c r="E5" t="n">
-        <v>50.383913</v>
+        <v>50.965207</v>
       </c>
       <c r="F5" t="n">
-        <v>103.129985</v>
+        <v>102.586407</v>
       </c>
       <c r="G5" t="n">
-        <v>0.092152</v>
+        <v>0.101697</v>
       </c>
       <c r="H5" t="n">
-        <v>44.608402</v>
+        <v>45.072193</v>
       </c>
     </row>
     <row r="6">
@@ -1541,16 +1541,16 @@
         <v>1870</v>
       </c>
       <c r="E6" t="n">
-        <v>47.136732</v>
+        <v>46.648119</v>
       </c>
       <c r="F6" t="n">
-        <v>80.124527</v>
+        <v>79.752487</v>
       </c>
       <c r="G6" t="n">
-        <v>0.077663</v>
+        <v>0.08620800000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>44.759939</v>
+        <v>44.436069</v>
       </c>
     </row>
   </sheetData>
@@ -1612,25 +1612,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.9091 ± 16.1880</t>
+          <t>53.9992 ± 15.8545</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>94.2384 ± 23.7759</t>
+          <t>94.1277 ± 23.2093</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.093349 ± 0.063093</t>
+          <t>0.093444 ± 0.050858</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>36.099666</v>
+        <v>36.074723</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38.6101 ~ 81.3407</t>
+          <t>39.4017 ~ 80.9311</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
